--- a/warranty_registry_backup.xlsx
+++ b/warranty_registry_backup.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/warranty_registry_backup.xlsx
+++ b/warranty_registry_backup.xlsx
@@ -507,6 +507,11 @@
           <t>2026-06-23 12:15:57</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
